--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/SOUTH_CAROLINA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/SOUTH_CAROLINA_2022.xlsx
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C242">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C251">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C679">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C680">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C715">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C720">
